--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 9/25）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 9/29）</t>
         </is>
       </c>
     </row>
@@ -1040,8 +1040,50 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" t="n">
-        <v>12</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>网站数据自动采集器</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>maxun（GitHub）</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>配置网址和字段→定时采集→自动对比变化（价格涨跌/新增/下架）→告警→导出CSV</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://aka.doubaocdn.com/s/jdmT6UyrBY</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1135,16 +1177,62 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 14 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AI目标驱动工作流执行器</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Beam AI（Product Hunt）</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>自然语言目标→AI拆解步骤链→调用虚拟工具逐步执行→产出交付物</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-09-29_AI目标驱动工作流工具/AI目标驱动工作流执行器.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 15 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A14:I14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 9/29）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 9/30）</t>
         </is>
       </c>
     </row>
@@ -1224,9 +1224,54 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 15 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Excel财务自动化助手</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Univer 1.0（GitHub）</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5星</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>自然语言指令→Agent填表/写公式/条件校验→导出CSV</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-09-30_Excel%E8%B4%A2%E5%8A%A1%E8%87%AA%E5%8A%A8%E5%8C%96%E5%8A%A9%E6%89%8B/Excel%E8%B4%A2%E5%8A%A1%E8%87%AA%E5%8A%A8%E5%8C%96%E5%8A%A9%E6%89%8B.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 16 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 9/30）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/01）</t>
         </is>
       </c>
     </row>
@@ -1269,9 +1269,54 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 16 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>业务流程可视化生成器</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Archify（GitHub）</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>中文描述业务流程→生成可点击交互式流程图→导出SVG/描述</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-01_%E4%B8%9A%E5%8A%A1%E6%B5%81%E7%A8%8B%E5%8F%AF%E8%A7%86%E5%8C%96%E7%94%9F%E6%88%90%E5%99%A8/%E4%B8%9A%E5%8A%A1%E6%B5%81%E7%A8%8B%E5%8F%AF%E8%A7%86%E5%8C%96%E7%94%9F%E6%88%90%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 17 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/01）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/02）</t>
         </is>
       </c>
     </row>
@@ -1314,9 +1314,54 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 17 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>自动化流程自积累工具</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GenericAgent（GitHub）</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5星</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>任务执行→自动沉淀为技能卡片→下次相似任务一键复用（执行/沉淀/复用闭环）</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-02_%E8%87%AA%E5%8A%A8%E5%8C%96%E6%B5%81%E7%A8%8B%E8%87%AA%E7%A7%AF%E7%B4%AF%E5%B7%A5%E5%85%B7/%E8%87%AA%E5%8A%A8%E5%8C%96%E6%B5%81%E7%A8%8B%E8%87%AA%E7%A7%AF%E7%B4%AF%E5%B7%A5%E5%85%B7.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 18 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/02）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/03）</t>
         </is>
       </c>
     </row>
@@ -1359,9 +1359,54 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 18 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Agent安全策略配置器</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OpenAPPA（GitHub）</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5星</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>业务表单定义数据级别与工具白名单→生成TOML策略→攻击场景模拟拦截/放行决策</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-03_Agent%E5%AE%89%E5%85%A8%E7%AD%96%E7%95%A5%E9%85%8D%E7%BD%AE%E5%99%A8/Agent%E5%AE%89%E5%85%A8%E7%AD%96%E7%95%A5%E9%85%8D%E7%BD%AE%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 19 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/03）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/04）</t>
         </is>
       </c>
     </row>
@@ -1404,9 +1404,54 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 19 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>多Agent团队编排配置器</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OpenRig（GitHub）</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>5星</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>业务表单定义主控与子Agent角色/依赖/汇报→生成YAML拓扑→模拟任务分发/结果收集/失败恢复</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-04_%E5%A4%9AAgent%E5%9B%A2%E9%98%9F%E7%BC%96%E6%8E%92%E9%85%8D%E7%BD%AE%E5%99%A8/%E5%A4%9AAgent%E5%9B%A2%E9%98%9F%E7%BC%96%E6%8E%92%E9%85%8D%E7%BD%AE%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 20 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/04）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/05）</t>
         </is>
       </c>
     </row>
@@ -1449,9 +1449,54 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 20 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>零拷贝数据自动化演示器</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>UiPath×Snowflake（其他）</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>5星</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>示例订单库存→配置自动化规则→对比传统ETL复制vs零拷贝直连→审计日志，讲清数据不动规则到数据边执行</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-05_%E9%9B%B6%E6%8B%B7%E8%B4%9D%E6%95%B0%E6%8D%AE%E8%87%AA%E5%8A%A8%E5%8C%96%E6%BC%94%E7%A4%BA%E5%99%A8/%E9%9B%B6%E6%8B%B7%E8%B4%9D%E6%95%B0%E6%8D%AE%E8%87%AA%E5%8A%A8%E5%8C%96%E6%BC%94%E7%A4%BA%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 21 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/05）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/06）</t>
         </is>
       </c>
     </row>
@@ -1494,9 +1494,54 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 21 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Agent操作审计台账</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Adobe Workfront Fusion（其他）</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5星</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>模拟Agent经MCP触发自动化场景全链路：每步留痕+破坏性操作弹审批卡，审计台账与治理</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-06_Agent%E6%93%8D%E4%BD%9C%E5%AE%A1%E8%AE%A1%E5%8F%B0%E8%B4%A6/Agent%E6%93%8D%E4%BD%9C%E5%AE%A1%E8%AE%A1%E5%8F%B0%E8%B4%A6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 22 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/06）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/07）</t>
         </is>
       </c>
     </row>
@@ -1539,9 +1539,54 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 22 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无API网站操作助手</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Hark Pro（其他）</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>自然语言任务→自动编排浏览器操作步骤→模拟执行（含截图验证与异常重试）→生成操作报告，演示无API系统的浏览器自动化</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-07_%E6%97%A0API%E7%BD%91%E7%AB%99%E6%93%8D%E4%BD%9C%E5%8A%A9%E6%89%8B/%E6%97%A0API%E7%BD%91%E7%AB%99%E6%93%8D%E4%BD%9C%E5%8A%A9%E6%89%8B.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 23 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/07）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/08）</t>
         </is>
       </c>
     </row>
@@ -1584,9 +1584,54 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 23 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Excel操作录制器</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IrisGo（Product Hunt）</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Excel/数据处理</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>模拟Excel手动操作（清洗/填充/汇总/透视）自动录制步骤并生成可复用pandas脚本，参数化+批量执行，降低Excel自动化门槛</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-08_Excel%E6%93%8D%E4%BD%9C%E5%BD%95%E5%88%B6%E5%99%A8/Excel%E6%93%8D%E4%BD%9C%E5%BD%95%E5%88%B6%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 24 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1629,9 +1629,56 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 24 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>会议行动项自动执行器</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Velozity（Product Hunt）</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>粘贴会议记录→提取行动项（负责人/任务/截止）→关键词匹配5个RPA流程（销售报表/回款催收/ERP录入/周报/报销），可下拉调整→单项或一键模拟执行并逐步记日志→统计卡跟踪</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-09_%E4%BC%9A%E8%AE%AE%E8%A1%8C%E5%8A%A8%E9%A1%B9%E8%87%AA%E5%8A%A8%E6%89%A7%E8%A1%8C%E5%99%A8/%E4%BC%9A%E8%AE%AE%E8%A1%8C%E5%8A%A8%E9%A1%B9%E8%87%AA%E5%8A%A8%E6%89%A7%E8%A1%8C%E5%99%A8_%E7%BD%91%E9%A1%B5%E7%89%88.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 25 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/08）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/10）</t>
         </is>
       </c>
     </row>
@@ -1676,9 +1676,54 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 25 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RPA流程安全网关</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Termaxa（Product Hunt）</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>静态分析脚本影响范围→风险分级→自动备份→高风险人工确认→不可篡改审计→一键回滚，让RPA敢跑能查可退</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-10_RPA%E6%B5%81%E7%A8%8B%E5%AE%89%E5%85%A8%E7%BD%91%E5%85%B3/RPA%E6%B5%81%E7%A8%8B%E5%AE%89%E5%85%A8%E7%BD%91%E5%85%B3.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 26 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1721,9 +1721,56 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 26 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RPA流程自适应执行器</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tester-army/e2e（GitHub）</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AI探索录制流程动作序列→零模型调用重放→页面改版自动检测→交回AI重新探索更新录制→重放恢复</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-11_RPA流程自适应执行器/RPA流程自适应执行器_网页版.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 27 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/10）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/12）</t>
         </is>
       </c>
     </row>
@@ -1768,9 +1768,54 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 27 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AI原生轻量RPA工具</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Perplexity Computer Automations（Product Hunt）</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>自然语言描述任务→AI自动拆解执行步骤→cron定时/Webhook触发→JSON记忆→重大操作人工确认→执行报告</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-12_AI%E5%8E%9F%E7%94%9F%E8%BD%BB%E9%87%8FRPA%E5%B7%A5%E5%85%B7/AI%E5%8E%9F%E7%94%9F%E8%BD%BB%E9%87%8FRPA%E5%B7%A5%E5%85%B7.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 28 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/12）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/13）</t>
         </is>
       </c>
     </row>
@@ -1813,9 +1813,54 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 28 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>聊天驱动的RPA助手</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OpenClaw（GitHub）</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>飞书/微信/命令行发自然语言指令→技能路由→工作流编排→cron调度→重大操作人工确认→结果聊天回执</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-13_%E8%81%8A%E5%A4%A9%E9%A9%B1%E5%8A%A8%E7%9A%84RPA%E5%8A%A9%E6%89%8B/%E8%81%8A%E5%A4%A9%E9%A9%B1%E5%8A%A8%E7%9A%84RPA%E5%8A%A9%E6%89%8B.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 29 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/13）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/14）</t>
         </is>
       </c>
     </row>
@@ -1858,9 +1858,54 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 29 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RPA后台任务管理器</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pizza Bot（AWS）</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>收件箱式多任务管理：任务入队→Worker分工→cron/Webhook触发→审批节点暂停→断点续跑/失败重试</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-14_RPA%E5%90%8E%E5%8F%B0%E4%BB%BB%E5%8A%A1%E7%AE%A1%E7%90%86%E5%99%A8/RPA%E5%90%8E%E5%8F%B0%E4%BB%BB%E5%8A%A1%E7%AE%A1%E7%90%86%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>说明：共 30 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1903,9 +1903,57 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>说明：共 30 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>RPA长任务无损记忆执行器</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Reflex Agent（APUS 开源）</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>任务模板逐步执行→每步完整中间结果写入JSONL无损记忆→中断后从记忆断点恢复不重跑→无损vs有损检索对比</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-15_RPA%E9%95%BF%E4%BB%BB%E5%8A%A1%E6%97%A0%E6%8D%9F%E8%AE%B0%E5%BF%86%E6%89%A7%E8%A1%8C%E5%99%A8/RPA%E9%95%BF%E4%BB%BB%E5%8A%A1%E6%97%A0%E6%8D%9F%E8%AE%B0%E5%BF%86%E6%89%A7%E8%A1%8C%E5%99%A8_%E7%BD%91%E9%A1%B5%E7%89%88.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>说明：共 31 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/14）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/16）</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,69 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n"/>
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RPA长任务无损记忆执行器</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Reflex Agent（APUS 开源）</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>任务模板逐步执行→每步完整中间结果写入JSONL无损记忆→中断后从记忆断点恢复不重跑→无损vs有损检索对比</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-15_RPA%E9%95%BF%E4%BB%BB%E5%8A%A1%E6%97%A0%E6%8D%9F%E8%AE%B0%E5%BF%86%E6%89%A7%E8%A1%8C%E5%99%A8/RPA%E9%95%BF%E4%BB%BB%E5%8A%A1%E6%97%A0%E6%8D%9F%E8%AE%B0%E5%BF%86%E6%89%A7%E8%A1%8C%E5%99%A8_%E7%BD%91%E9%A1%B5%E7%89%88.html</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RPA长任务无损记忆执行器</t>
+          <t>RPA技能市场</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Reflex Agent（APUS 开源）</t>
+          <t>CowAgent（GitHub）</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1936,7 +1980,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>任务模板逐步执行→每步完整中间结果写入JSONL无损记忆→中断后从记忆断点恢复不重跑→无损vs有损检索对比</t>
+          <t>自然语言描述需求→自动生成RPA技能→模板库一键安装→测试验证→执行日志监控+失败重试</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1946,14 +1990,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-15_RPA%E9%95%BF%E4%BB%BB%E5%8A%A1%E6%97%A0%E6%8D%9F%E8%AE%B0%E5%BF%86%E6%89%A7%E8%A1%8C%E5%99%A8/RPA%E9%95%BF%E4%BB%BB%E5%8A%A1%E6%97%A0%E6%8D%9F%E8%AE%B0%E5%BF%86%E6%89%A7%E8%A1%8C%E5%99%A8_%E7%BD%91%E9%A1%B5%E7%89%88.html</t>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-16_RPA%E6%8A%80%E8%83%BD%E5%B8%82%E5%9C%BA/RPA%E6%8A%80%E8%83%BD%E5%B8%82%E5%9C%BA.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>说明：共 31 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+          <t>说明：共 32 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1995,9 +1995,54 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>说明：共 32 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RPA流程自动沉淀与进化器</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Hermes Agent（Nous Research）</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>流程执行→AI自动总结沉淀v1模板→2次执行触发进化分析（合并步骤/预置异常处理/预取参数）→升级v2模板→执行提速34%异常清零</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-17_RPA%E6%B5%81%E7%A8%8B%E8%87%AA%E5%8A%A8%E6%B2%89%E6%B7%80%E4%B8%8E%E8%BF%9B%E5%8C%96%E5%99%A8/RPA%E6%B5%81%E7%A8%8B%E8%87%AA%E5%8A%A8%E6%B2%89%E6%B7%80%E4%B8%8E%E8%BF%9B%E5%8C%96%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>说明：共 33 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2040,9 +2040,54 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>说明：共 33 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>RPA多任务并行执行控制台</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Orca Agent Fleet Manager（GitHub）</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>参考Orca多Agent并行模式：4个RPA任务并行执行（价格采集/Excel报表/发票核对/邮件分发）→独立沙箱隔离→手机远程监控→执行前后diff对比→异常一键干预（暂停/继续/重跑）</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-18_RPA%E5%A4%9A%E4%BB%BB%E5%8A%A1%E5%B9%B6%E8%A1%8C%E6%89%A7%E8%A1%8C%E6%8E%A7%E5%88%B6%E5%8F%B0/RPA%E5%A4%9A%E4%BB%BB%E5%8A%A1%E5%B9%B6%E8%A1%8C%E6%89%A7%E8%A1%8C%E6%8E%A7%E5%88%B6%E5%8F%B0.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>说明：共 34 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2087,7 +2087,54 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>说明：共 34 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RPA最少步骤流程生成器</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ponytail 5（GitHub）</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>参考ponytail最少代码理念：AI原始方案→逐条砍掉过度设计（装库/抽象层/wrapper）→最少步骤方案（9步→4步压缩56%）→强制风险说明（跳过了什么/你必须知道）→lite/full/ultra三档模式→流程存模板库复用</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-19_RPA%E6%9C%80%E5%B0%91%E6%AD%A5%E9%AA%A4%E6%B5%81%E7%A8%8B%E7%94%9F%E6%88%90%E5%99%A8/RPA%E6%9C%80%E5%B0%91%E6%AD%A5%E9%AA%A4%E6%B5%81%E7%A8%8B%E7%94%9F%E6%88%90%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>说明：共 35 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -2085,10 +2085,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A37" t="n">
+        <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2117,7 +2115,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>参考ponytail最少代码理念：AI原始方案→逐条砍掉过度设计（装库/抽象层/wrapper）→最少步骤方案（9步→4步压缩56%）→强制风险说明（跳过了什么/你必须知道）→lite/full/ultra三档模式→流程存模板库复用</t>
+          <t>参考ponytail最少代码理念：需求→规则引擎匹配→AI原始方案逐条砍掉过度设计（装库/抽象层/wrapper）→最少步骤方案（8步→4步压缩50%）→强制风险说明（跳过什么/必须知道）→lite/full/ultra三档→模板库复用</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2133,6 +2133,58 @@
       <c r="A38" t="inlineStr">
         <is>
           <t>说明：共 35 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AI浏览器RPA自愈执行器</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Microsoft Playwright AI agent CLI（GitHub）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>参考Playwright三agent架构：可访问性树结构化理解页面（22节点）→Planner定计划→Generator生成getByRole代码→执行中途注入改版A/B→定位失败时Healer语义匹配自动重找元素并重试→零人工维护选择器（与10/11录制重放路线对照）</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-20_AI%E6%B5%8F%E8%A7%88%E5%99%A8RPA%E8%87%AA%E6%84%88%E6%89%A7%E8%A1%8C%E5%99%A8/AI%E6%B5%8F%E8%A7%88%E5%99%A8RPA%E8%87%AA%E6%84%88%E6%89%A7%E8%A1%8C%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>说明：共 36 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2130,59 +2130,52 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>说明：共 35 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AI浏览器RPA自愈执行器</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Microsoft Playwright AI agent CLI（GitHub）</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>参考Playwright三agent架构：自然语言任务→Planner解析意图（目标/站点/数据/策略）→Generator基于可访问性树快照生成步骤（goto/wait/extract/fill/click/assert）→执行模拟→首个可失败点注入定位失败→Healer诊断原因+打补丁+重试成功→4任务模板（价格采集/订单监控/表单填写/数据回填）+通用兜底→localStorage统计持久化</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-20_AI%E6%B5%8F%E8%A7%88%E5%99%A8RPA%E8%87%AA%E6%84%88%E6%89%A7%E8%A1%8C%E5%99%A8/AI%E6%B5%8F%E8%A7%88%E5%99%A8RPA%E8%87%AA%E6%84%88%E6%89%A7%E8%A1%8C%E5%99%A8.html</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AI浏览器RPA自愈执行器</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Microsoft Playwright AI agent CLI（GitHub）</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>4星</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>网页工具</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>参考Playwright三agent架构：可访问性树结构化理解页面（22节点）→Planner定计划→Generator生成getByRole代码→执行中途注入改版A/B→定位失败时Healer语义匹配自动重找元素并重试→零人工维护选择器（与10/11录制重放路线对照）</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>已交付</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-20_AI%E6%B5%8F%E8%A7%88%E5%99%A8RPA%E8%87%AA%E6%84%88%E6%89%A7%E8%A1%8C%E5%99%A8/AI%E6%B5%8F%E8%A7%88%E5%99%A8RPA%E8%87%AA%E6%84%88%E6%89%A7%E8%A1%8C%E5%99%A8.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>说明：共 36 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2175,9 +2175,54 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>说明：共 36 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RPA流程自动调优器</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Google Research 开源 Harness²（GitHub）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>参考Harness²两层递归+Propose-Probe-Compose：多方案生成（3候选·不同步骤/工具/异常策略）→并行探测（沙箱执行·成功率/耗时/异常率）→行为对比（自动标注优势片段·无标准答案）→自动重组（提取最优部分合成优化版v2·耗时/成功率双提升）→经验积累（策略入库localStorage·相似任务自动推荐·第二层递归）→透明审计决策日志；4业务模板+通用兜底</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-21_RPA%E6%B5%81%E7%A8%8B%E8%87%AA%E5%8A%A8%E8%B0%83%E4%BC%98%E5%99%A8/RPA%E6%B5%81%E7%A8%8B%E8%87%AA%E5%8A%A8%E8%B0%83%E4%BC%98%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>说明：共 37 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2220,9 +2220,54 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>说明：共 37 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>主动式RPA任务发现执行器</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Anthropic Claude Duet 主动式AI代理</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>参考Claude Duet主动扫描+云端持续运行+安全护栏：①主动扫描4数据源（邮件/飞书/Excel/ERP）发现待办事项②自动执行——非敏感任务发现即触发RPA流程（云端心跳650ms并行推进）③敏感操作（付款/改数据/权限回收）自动暂停待人工审批④敏感信息自动脱敏⑤任务看板——批准/驳回/暂停/继续/跳过人工干预⑥学习优化——每次决策沉淀规则库；10任务模板+脱敏引擎+规则去重</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-22_%E4%B8%BB%E5%8A%A8%E5%BC%8FRPA%E4%BB%BB%E5%8A%A1%E5%8F%91%E7%8E%B0%E6%89%A7%E8%A1%8C%E5%99%A8/%E4%B8%BB%E5%8A%A8%E5%BC%8FRPA%E4%BB%BB%E5%8A%A1%E5%8F%91%E7%8E%B0%E6%89%A7%E8%A1%8C%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>说明：共 38 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/16）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/23）</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,54 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>说明：共 38 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AI编译式RPA流程生成器</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Airtop 编译式浏览器 agent</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>自然语言需求→AI规划拆步→编译成确定性流程代码→运行零LLM调用→改版自愈修复重新编译v1.1（与Agent模式成本对照）</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-23_AI%E7%BC%96%E8%AF%91%E5%BC%8FRPA%E6%B5%81%E7%A8%8B%E7%94%9F%E6%88%90%E5%99%A8/AI%E7%BC%96%E8%AF%91%E5%BC%8FRPA%E6%B5%81%E7%A8%8B%E7%94%9F%E6%88%90%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>说明：共 39 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,7 +493,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 小工具 Demo 台账（9/14 – 10/23）</t>
+          <t>AI 小工具 Demo 台账（9/14 – 10/16）</t>
         </is>
       </c>
     </row>
@@ -2265,10 +2265,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A41" t="n">
+        <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2282,7 +2280,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Airtop 编译式浏览器 agent</t>
+          <t>Airtop 自然语言→确定性浏览器agent</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2297,7 +2295,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>自然语言需求→AI规划拆步→编译成确定性流程代码→运行零LLM调用→改版自愈修复重新编译v1.1（与Agent模式成本对照）</t>
+          <t>自然语言描述自动化需求→AI编译生成确定性流程代码（非每次推理）→确定性执行引擎逐步运行（600ms心跳，编译一次稳定跑）→自愈机制（外部步骤失效时AI重新定位选择器/接口并自动修复，跳过/修复人工可干预）→可视化Trace步骤级审计日志可回放→定时运行记录+本地保存复用；4业务模板（ERP日报/发票提醒/库存预警/对账核对）+编译规则库</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2310,9 +2310,54 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>说明：共 39 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>RPA流程决策记忆库</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Trail-Code 代码地图+团队决策记忆</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>参考 Trail-Code「代码地图+决策记忆」两层架构：①流程地图——纯规则解析 RPA 流程结构（步骤/依赖/异常分支）可视化，无模型无网络；②决策记忆——设计决策+踩坑经验，个人存本地团队随流程走，关键记忆可锁定；③冲突检测——模拟队友编辑中，新增记忆与锁定记忆同节点/同标签/内容重叠时警告「你在撤销之前的设计决策」并写入冲突日志；④自动初始化——从执行日志按规则匹配去重自动沉淀经验；⑤经验检索——关键词/标签近似匹配+相似流程按标签重合度推荐；3示例流程+5预置记忆+5日志，localStorage 保存复用</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-24_RPA%E6%B5%81%E7%A8%8B%E5%86%B3%E7%AD%96%E8%AE%B0%E5%BF%86%E5%BA%93/RPA%E6%B5%81%E7%A8%8B%E5%86%B3%E7%AD%96%E8%AE%B0%E5%BF%86%E5%BA%93.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>说明：共 40 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2355,9 +2355,54 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>说明：共 40 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RPA全流程审计回放平台</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BrowserOS 登录态+Session回放+MCP驱动</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>参考 BrowserOS「现有登录态+Session 视频回放+MCP 驱动」：①登录态管理——3 个企业系统会话（ERP/供应商门户/工单系统），真实账号身份操作，MFA/验证码自动创建人工介入点，标记可持久化；②流程回放——执行记录含逐步操作时间线（操作/选择器/耗时），失败步骤标红，播放/暂停/慢放逐帧回放；③异常诊断——失败步骤按规则库自动诊断（选择器失效/超时/登录过期/反爬）+修复建议，可重新诊断生成复诊结论；④并行任务——4 流程独立会话并发，进度条推进+状态机（待启动/运行中/已完成/失败/待人工介入）⑤合规审计——审计日志留痕（谁/何时/做了什么），敏感操作高亮，一键导出审计报告；localStorage 保存介入点标记</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-25_RPA%E5%85%A8%E6%B5%81%E7%A8%8B%E5%AE%A1%E8%AE%A1%E5%9B%9E%E6%94%BE%E5%B9%B3%E5%8F%B0/RPA%E5%85%A8%E6%B5%81%E7%A8%8B%E5%AE%A1%E8%AE%A1%E5%9B%9E%E6%94%BE%E5%B9%B3%E5%8F%B0.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>说明：共 41 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2400,9 +2400,54 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>说明：共 41 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RPA流程运行时守护器</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Herdr session保活+三态监控+阻塞通知+agent间编排</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>参考 Herdr「session 保活+三态标记+阻塞通知+agent 间编排」（45.7K stars，Rust 终端运行时）：①守护总览——5 个 RPA 流程各自独立后台 session，3s 心跳存活计时，状态徽标（运行中/阻塞/待触发/失败）；②断线保活——模拟 SSH 断开/客户端关闭，后台继续推进进度不丢，重连显示断线期间推进量；③三态监控+阻塞通知——流程阻塞（验证码/MFA/异常）自动暂停保存上下文，横幅通知（飞书/邮件/短信）；④人工介入——介入面板含上下文快照（当前步骤/选择器/页面状态），处理后可断点续跑不从头重跑；⑤流程编排——DAG 依赖链（日报导出→发票核验→库存预警，对账单并行），一键推进模拟调度触发；⑥执行日志——逐步回放+失败步骤精确定位；保活/介入/编排全链路可观测</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-26_RPA%E6%B5%81%E7%A8%8B%E8%BF%90%E8%A1%8C%E6%97%B6%E5%AE%88%E6%8A%A4%E5%99%A8/RPA%E6%B5%81%E7%A8%8B%E8%BF%90%E8%A1%8C%E6%97%B6%E5%AE%88%E6%8A%A4%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>说明：共 42 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2445,9 +2445,54 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>说明：共 42 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AI热点日报生成器</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AIHOT信源收集+LLM筛选双评分+事件聚簇+每日出报</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>参考 AIHOT「信源收集+LLM 筛选双评分+事件聚簇+每日出报」（8.6K stars，自动化热点日报框架）：①信源采集——8 个信源（Product Hunt/GitHub Trending/36氪/Hacker News/Reddit/量子位/InfoQ/少数派）自动抓取入库，模拟逐源采集耗时与进度；②双评分筛选——热度×0.5+相关度×0.5（相关度按用户画像词库加权：RPA/AI落地/数字化运营/数据分析/效率工具），阈值滑块实时调节入选线；③事件聚簇——标题关键词匹配（Agent/RPA/日报/中台/融资等）自动合并同主题资讯，避免日报重复刷屏；④日报生成——每日 08:00 自动出报：今日头条+榜单 Top5+信源分布统计，一键复制 Markdown 可直接粘贴到飞书文档/公众号；⑤定时推送——自动出报开关+飞书/邮件/钉钉渠道配置+推送日志；运营人每天早上 10 分钟读完行业热点</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-27_AI%E7%83%AD%E7%82%B9%E6%97%A5%E6%8A%A5%E7%94%9F%E6%88%90%E5%99%A8/AI%E7%83%AD%E7%82%B9%E6%97%A5%E6%8A%A5%E7%94%9F%E6%88%90%E5%99%A8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>说明：共 43 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2490,9 +2490,54 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>说明：共 43 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LLM API成本监控面板</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FreeLLMAPI 34家免费provider聚合+智能路由+故障转移</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>参考 FreeLLMAPI「34家免费provider聚合+智能路由+故障转移」（41K stars，自托管LLM路由，每月74亿免费token）：①统一端点——所有 AI 应用（客服机器人/文档处理/数据分析/RPA 智能环节）只配一个 OpenAI 兼容端点，路由与故障转移由网关完成、应用零改动；②Provider 路由总览——8 家 provider（OpenAI/DeepSeek/Gemini/通义/Kimi/Claude/智谱/文心）单价、延迟、免费配额、可用状态可视化；③智能路由——按策略（最低单价/最低延迟/轮询均衡）自动选 Provider，测试请求日志记录每次决策理由；④故障转移——Provider 故障自动绕行切换、请求 0 失败，支持手动模拟故障与一键恢复；⑤成本监控——近 12 天 token 用量趋势图（SVG 柱状）、按 Provider 配额分布、月度成本与预算实时比对；⑥配额预算——74 亿免费 token 配额进度条（占用&gt;80% 预警、&gt;95% 强制降级），月度预算上限+超限告警；把公司 AI 应用 API 成本管起来</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-28_LLM%20API%E6%88%90%E6%9C%AC%E7%9B%91%E6%8E%A7%E9%9D%A2%E6%9D%BF/LLM%20API%E6%88%90%E6%9C%AC%E7%9B%91%E6%8E%A7%E9%9D%A2%E6%9D%BF.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>说明：共 44 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2535,9 +2535,54 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>说明：共 44 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>微信消息自动建单助手</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EntryFilter AI现场数据采集：语音/照片/聊天→ERP结构化数据</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>参考 EntryFilter「AI现场数据采集层：语音笔记/照片/聊天自动清洗成ERP结构化数据」（Product Hunt 新上线）：①消息输入——支持三种来源（文字/语音转写/拍照OCR）模拟群消息，销售在群里发『客户王老板要了10箱可乐，送到A仓库』直接入库解析；②AI字段抽取——模拟LLM从消息中提取客户名/商品/数量/单位/目的地/送达时间 6 字段，缺失项标黄提示；③销售出库单草稿——抽取结果自动组装成出库单草稿（客户/商品明细/数量/目的地/送达时间），支持提交/驳回流转，缺字段草稿拦截提交；④状态管理——已处理消息/成功建单/待补全/抽取成功率四维统计；把『聊天→手工抄单→ERP录入』三步压成一步，销售与仓库实时联动</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-29_%E5%BE%AE%E4%BF%A1%E6%B6%88%E6%81%AF%E8%87%AA%E5%8A%A8%E5%BB%BA%E5%8D%95%E5%8A%A9%E6%89%8B/%E5%BE%AE%E4%BF%A1%E6%B6%88%E6%81%AF%E8%87%AA%E5%8A%A8%E5%BB%BA%E5%8D%95%E5%8A%A9%E6%89%8B.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>说明：共 45 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>

--- a/demos/作品集总览/AI小工具Demo台账.xlsx
+++ b/demos/作品集总览/AI小工具Demo台账.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2580,9 +2580,54 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>说明：共 45 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>门店一键操作助手</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>OmniGlass 把MCP工具变成一线工人一键点击的OS级按钮，不用对话</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4星</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>网页工具</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>参考 OmniGlass「把MCP工具变成一线工人一键点击的OS级按钮，不用对话」（Rust/Tauri开源，HN 4星）：①大按钮面板——门店店长不用面对复杂ERP，只看4个大按钮（今日收货/盘点提交/报损登记/交接班）；②截屏理解——点按钮后助手自动识别当前ERP表单哪些字段已填、哪些为空（空字段标黄）；③AI自动填——模拟OCR+LLM按业务规则自动填入默认值（供应商/实收数量/收货金额自动计算/差异原因/交接待办），带置信度；④提交流转——字段齐全才能提交，缺字段拦截，提交后任务状态更新；⑤四维统计——今日完成数/AI填充字段/节省时间/拦截次数；把『翻菜单→手工填表→提交』压成『点按钮→一键填充→提交』，餐饮连锁门店数字化运营的典型场景</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>已交付</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://github.com/zhonghugo/Hugo-AI-Tools-Demos/blob/main/demos/2026-10-31_%E9%97%A8%E5%BA%97%E4%B8%80%E9%94%AE%E6%93%8D%E4%BD%9C%E5%8A%A9%E6%89%8B/%E9%97%A8%E5%BA%97%E4%B8%80%E9%94%AE%E6%93%8D%E4%BD%9C%E5%8A%A9%E6%89%8B.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>说明：共 46 个已交付 demo；9/22 因当日无资讯入库未产出；来源均为「AI工具资讯日报」飞书多维表格，点击链接可直接打开运行。</t>
         </is>
       </c>
     </row>
